--- a/intake_forms/046_end_of_life_care_plan--intake_forms.xlsx
+++ b/intake_forms/046_end_of_life_care_plan--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page_label</t>
+          <t>Patient's Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>personal_information</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>personal_information</t>
+          <t>Personal Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,35 +566,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social_support</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>social_support</t>
+          <t>Medical Caregivers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_caregivers</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medical_caregivers</t>
+          <t>Medical Caregivers List</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_caregivers_list</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medical_caregivers_list</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>Medical Conditions List</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medications_list</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medications_list</t>
+          <t>Medications List</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>Allergies</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>advance_directives</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>advance_directives</t>
+          <t>Allergies List</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>advance_directives_list</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>advance_directives_list</t>
+          <t>Advance Directives</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_caregivers_other</t>
+          <t>page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>other_caregivers</t>
+          <t>Advance Directives List</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medical_caregivers_other_list</t>
+          <t>page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>other_caregivers_list</t>
+          <t>Other Caregivers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_conditions_other</t>
+          <t>page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>other_conditions</t>
+          <t>Other Caregivers List</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_conditions_other_list</t>
+          <t>page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>other_conditions_list</t>
+          <t>Other Medical Conditions</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medications_other</t>
+          <t>page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>other_medications</t>
+          <t>Other Medical Conditions List</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medications_other_list</t>
+          <t>page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>other_medications_list</t>
+          <t>Other Medications</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>advance_directives_other</t>
+          <t>page_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>other_advanceประกirectives</t>
+          <t>Other Medications List</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,23 +952,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>advance_directives_other_list</t>
+          <t>page_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>other_advance_directives_list</t>
+          <t>Review and Acknowledgement</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other_caregivers</t>
+          <t>page_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>other_caregivers</t>
+          <t>Review and Acknowledgement List</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other_caregivers_list</t>
+          <t>page_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>other_caregivers_list</t>
+          <t>Other Information</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other_conditions</t>
+          <t>page_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>other_conditions</t>
+          <t>Other Information List</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other_conditions_list</t>
+          <t>page_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>other_conditions_list</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other_medications</t>
+          <t>page_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>other_medications</t>
+          <t>Additional Comments List</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>medical_caregivers_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>medical_caregivers_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>medical_caregivers_list_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>medical_caregivers_list_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medications_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medications_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medications_list_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medications_list_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>page_16_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>page_16_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>advance_directives_choices</t>
+          <t>page_18_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>advance_directives_choices</t>
+          <t>page_18_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1356,312 +1356,6 @@
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>advance_directives_list_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>advance_directives_list_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medical_caregivers_other_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medical_caregivers_other_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medical_caregivers_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>medical_caregivers_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>medical_conditions_other_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>medical_conditions_other_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>medical_conditions_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>medical_conditions_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>medications_other_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>medications_other_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>medications_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>medications_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>advance_directives_other_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>advance_directives_other_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>advance_directives_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>advance_directives_other_list_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
